--- a/statements/January_2026_20260124_215553.xlsx
+++ b/statements/January_2026_20260124_215553.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dell-my.sharepoint.com/personal/sonit_mehrotra_dell_com/Documents/Desktop/Personal/Sbi-excel-writing-script/statements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_07EB3223CB4A16F7C26C317F8572B11F0BF92160" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8AE9E8B-CD4E-4D0A-8473-109C4EDB36D3}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_07EB3223CB4A16F7C26C317F8572B11F0BF92160" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95FF4058-C904-4151-A5DA-C71EC1AE4DCE}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -241,6 +241,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,6 +551,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="53.20703125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
